--- a/output/pdf_financials_xlsx/HITI.xlsx
+++ b/output/pdf_financials_xlsx/HITI.xlsx
@@ -748,19 +748,19 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5.535</v>
+        <v>82.657</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>11.384</v>
+        <v>173.262</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.643000000000001</v>
+        <v>172.739</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>9.515000000000001</v>
+        <v>137.499</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>9.506</v>
+        <v>167.978</v>
       </c>
     </row>
     <row r="11">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -27317,19 +27317,19 @@
         <v>-31.19</v>
       </c>
       <c r="H403" s="5" t="n">
-        <v>-82.657</v>
+        <v>82.657</v>
       </c>
       <c r="I403" s="5" t="n">
-        <v>-173.262</v>
+        <v>173.262</v>
       </c>
       <c r="J403" s="5" t="n">
-        <v>-172.739</v>
+        <v>172.739</v>
       </c>
       <c r="K403" s="5" t="n">
-        <v>-137.499</v>
+        <v>137.499</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>-167.978</v>
+        <v>167.978</v>
       </c>
     </row>
     <row r="404">

--- a/output/pdf_financials_xlsx/HITI.xlsx
+++ b/output/pdf_financials_xlsx/HITI.xlsx
@@ -2562,19 +2562,19 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>8.739000000000001</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>7.67</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>8.353</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>8.055</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>27.765</v>
       </c>
     </row>
     <row r="65">
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.033381</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.869462</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>7.256</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>26.246</v>
@@ -2667,7 +2667,7 @@
         <v>23.809</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>12.484</v>
       </c>
     </row>
     <row r="68">
@@ -2692,7 +2692,7 @@
         <v>26.887</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>20.902</v>
+        <v>29.255</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>22.15</v>
@@ -2909,7 +2909,7 @@
         <v>24.784</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>28.66</v>
+        <v>20.307</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>28.524</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>1.476</v>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
@@ -4021,16 +4021,16 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>4.766</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>4.338</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>4.392</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="111">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.483937</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -4164,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.646</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-2.333</v>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
@@ -4231,16 +4231,16 @@
         </is>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-1.296</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.295</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.703</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="117">
@@ -5546,7 +5546,11 @@
           <t>Intangible assets and goodwill 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -9456,7 +9460,11 @@
           <t>Intangible assets and goodwill 5,8</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -10822,7 +10830,11 @@
           <t>Intangible assets and goodwill 7</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -17236,7 +17248,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -17286,7 +17302,11 @@
           <t>Accretion expense 19</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -18430,7 +18450,11 @@
           <t>Purchase of intangible assets 8</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -19788,7 +19812,11 @@
           <t>Accretion expense 18</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -20616,7 +20644,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -21278,7 +21310,11 @@
           <t>Accretion expense 17</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -21998,7 +22034,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -22722,7 +22762,11 @@
           <t>Accretion 14</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -22834,7 +22878,11 @@
           <t>Impairment loss on goodwill 7</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -23734,7 +23782,11 @@
           <t>Purchase of intangible assets 7</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -24066,7 +24118,11 @@
           <t>Net proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -25896,7 +25952,11 @@
           <t>Purchase of marketable securities -</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -26348,7 +26408,11 @@
           <t>Net proceeds from share issuance (Note 15) 3,887,353</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -27892,7 +27956,11 @@
           <t>Deferred income tax recovery 20</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -29304,7 +29372,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -30462,7 +30534,11 @@
           <t>Income tax recovery (expense) 18</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -30516,7 +30592,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
